--- a/Datos problema doblaje(30 tomas, 10 actores).xlsx
+++ b/Datos problema doblaje(30 tomas, 10 actores).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\victo\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D55F7B84-E57E-403F-8E98-8C9737BA0EDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62E27333-0F81-402F-8148-2CCDCB73C96E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -326,15 +326,14 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:M35"/>
+  <dimension ref="A1:L35"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="11" width="4" customWidth="1"/>
-    <col min="12" max="12" width="5.77734375" customWidth="1"/>
-    <col min="13" max="13" width="6.33203125" customWidth="1"/>
+    <col min="12" max="12" width="6.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="7" t="s">
         <v>0</v>
@@ -349,9 +348,8 @@
       <c r="J1" s="8"/>
       <c r="K1" s="8"/>
       <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -385,12 +383,11 @@
       <c r="K2" s="3">
         <v>10</v>
       </c>
-      <c r="L2" s="1"/>
-      <c r="M2" s="2" t="s">
+      <c r="L2" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
         <v>1</v>
       </c>
@@ -424,12 +421,11 @@
       <c r="K3" s="5">
         <v>0</v>
       </c>
-      <c r="L3" s="6"/>
-      <c r="M3" s="5">
+      <c r="L3" s="5">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>2</v>
       </c>
@@ -463,12 +459,11 @@
       <c r="K4" s="5">
         <v>0</v>
       </c>
-      <c r="L4" s="6"/>
-      <c r="M4" s="5">
+      <c r="L4" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>3</v>
       </c>
@@ -502,12 +497,11 @@
       <c r="K5" s="5">
         <v>0</v>
       </c>
-      <c r="L5" s="6"/>
-      <c r="M5" s="5">
+      <c r="L5" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>4</v>
       </c>
@@ -541,12 +535,11 @@
       <c r="K6" s="5">
         <v>0</v>
       </c>
-      <c r="L6" s="6"/>
-      <c r="M6" s="5">
+      <c r="L6" s="5">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>5</v>
       </c>
@@ -580,12 +573,11 @@
       <c r="K7" s="5">
         <v>0</v>
       </c>
-      <c r="L7" s="6"/>
-      <c r="M7" s="5">
+      <c r="L7" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <v>6</v>
       </c>
@@ -619,12 +611,11 @@
       <c r="K8" s="5">
         <v>0</v>
       </c>
-      <c r="L8" s="6"/>
-      <c r="M8" s="5">
+      <c r="L8" s="5">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <v>7</v>
       </c>
@@ -658,12 +649,11 @@
       <c r="K9" s="5">
         <v>0</v>
       </c>
-      <c r="L9" s="6"/>
-      <c r="M9" s="5">
+      <c r="L9" s="5">
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <v>8</v>
       </c>
@@ -697,12 +687,11 @@
       <c r="K10" s="5">
         <v>0</v>
       </c>
-      <c r="L10" s="6"/>
-      <c r="M10" s="5">
+      <c r="L10" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <v>9</v>
       </c>
@@ -736,12 +725,11 @@
       <c r="K11" s="5">
         <v>0</v>
       </c>
-      <c r="L11" s="6"/>
-      <c r="M11" s="5">
+      <c r="L11" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
         <v>10</v>
       </c>
@@ -775,12 +763,11 @@
       <c r="K12" s="5">
         <v>0</v>
       </c>
-      <c r="L12" s="6"/>
-      <c r="M12" s="5">
+      <c r="L12" s="5">
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <v>11</v>
       </c>
@@ -814,12 +801,11 @@
       <c r="K13" s="5">
         <v>0</v>
       </c>
-      <c r="L13" s="6"/>
-      <c r="M13" s="5">
+      <c r="L13" s="5">
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
         <v>12</v>
       </c>
@@ -853,12 +839,11 @@
       <c r="K14" s="5">
         <v>0</v>
       </c>
-      <c r="L14" s="6"/>
-      <c r="M14" s="5">
+      <c r="L14" s="5">
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
         <v>13</v>
       </c>
@@ -892,12 +877,11 @@
       <c r="K15" s="5">
         <v>0</v>
       </c>
-      <c r="L15" s="6"/>
-      <c r="M15" s="5">
+      <c r="L15" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
         <v>14</v>
       </c>
@@ -931,12 +915,11 @@
       <c r="K16" s="5">
         <v>0</v>
       </c>
-      <c r="L16" s="6"/>
-      <c r="M16" s="5">
+      <c r="L16" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
         <v>15</v>
       </c>
@@ -970,12 +953,11 @@
       <c r="K17" s="5">
         <v>0</v>
       </c>
-      <c r="L17" s="6"/>
-      <c r="M17" s="5">
+      <c r="L17" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
         <v>16</v>
       </c>
@@ -1009,12 +991,11 @@
       <c r="K18" s="5">
         <v>1</v>
       </c>
-      <c r="L18" s="6"/>
-      <c r="M18" s="5">
+      <c r="L18" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
         <v>17</v>
       </c>
@@ -1048,12 +1029,11 @@
       <c r="K19" s="5">
         <v>0</v>
       </c>
-      <c r="L19" s="6"/>
-      <c r="M19" s="5">
+      <c r="L19" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="4">
         <v>18</v>
       </c>
@@ -1087,12 +1067,11 @@
       <c r="K20" s="5">
         <v>0</v>
       </c>
-      <c r="L20" s="6"/>
-      <c r="M20" s="5">
+      <c r="L20" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
         <v>19</v>
       </c>
@@ -1126,12 +1105,11 @@
       <c r="K21" s="5">
         <v>0</v>
       </c>
-      <c r="L21" s="6"/>
-      <c r="M21" s="5">
+      <c r="L21" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
         <v>20</v>
       </c>
@@ -1165,12 +1143,11 @@
       <c r="K22" s="5">
         <v>0</v>
       </c>
-      <c r="L22" s="6"/>
-      <c r="M22" s="5">
+      <c r="L22" s="5">
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
         <v>21</v>
       </c>
@@ -1204,12 +1181,11 @@
       <c r="K23" s="5">
         <v>0</v>
       </c>
-      <c r="L23" s="6"/>
-      <c r="M23" s="5">
+      <c r="L23" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="4">
         <v>22</v>
       </c>
@@ -1243,12 +1219,11 @@
       <c r="K24" s="5">
         <v>0</v>
       </c>
-      <c r="L24" s="6"/>
-      <c r="M24" s="5">
+      <c r="L24" s="5">
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
         <v>23</v>
       </c>
@@ -1282,12 +1257,11 @@
       <c r="K25" s="5">
         <v>0</v>
       </c>
-      <c r="L25" s="6"/>
-      <c r="M25" s="5">
+      <c r="L25" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="4">
         <v>24</v>
       </c>
@@ -1321,12 +1295,11 @@
       <c r="K26" s="5">
         <v>0</v>
       </c>
-      <c r="L26" s="6"/>
-      <c r="M26" s="5">
+      <c r="L26" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="4">
         <v>25</v>
       </c>
@@ -1360,12 +1333,11 @@
       <c r="K27" s="5">
         <v>1</v>
       </c>
-      <c r="L27" s="6"/>
-      <c r="M27" s="5">
+      <c r="L27" s="5">
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="4">
         <v>26</v>
       </c>
@@ -1399,12 +1371,11 @@
       <c r="K28" s="5">
         <v>0</v>
       </c>
-      <c r="L28" s="6"/>
-      <c r="M28" s="5">
+      <c r="L28" s="5">
         <v>4</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="4">
         <v>27</v>
       </c>
@@ -1438,12 +1409,11 @@
       <c r="K29" s="5">
         <v>0</v>
       </c>
-      <c r="L29" s="6"/>
-      <c r="M29" s="5">
+      <c r="L29" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="4">
         <v>28</v>
       </c>
@@ -1477,12 +1447,11 @@
       <c r="K30" s="5">
         <v>0</v>
       </c>
-      <c r="L30" s="6"/>
-      <c r="M30" s="5">
+      <c r="L30" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="4">
         <v>29</v>
       </c>
@@ -1516,12 +1485,11 @@
       <c r="K31" s="5">
         <v>0</v>
       </c>
-      <c r="L31" s="6"/>
-      <c r="M31" s="5">
+      <c r="L31" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" s="4">
         <v>30</v>
       </c>
@@ -1555,12 +1523,11 @@
       <c r="K32" s="5">
         <v>0</v>
       </c>
-      <c r="L32" s="6"/>
-      <c r="M32" s="5">
+      <c r="L32" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
         <v>3</v>
       </c>
@@ -1595,9 +1562,8 @@
         <v>2</v>
       </c>
       <c r="L33" s="6"/>
-      <c r="M33" s="6"/>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" s="6"/>
       <c r="B34" s="6"/>
       <c r="C34" s="6"/>
@@ -1610,9 +1576,8 @@
       <c r="J34" s="6"/>
       <c r="K34" s="6"/>
       <c r="L34" s="6"/>
-      <c r="M34" s="6"/>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" s="6"/>
       <c r="B35" s="6"/>
       <c r="C35" s="6"/>
@@ -1625,12 +1590,12 @@
       <c r="J35" s="6"/>
       <c r="K35" s="6"/>
       <c r="L35" s="6"/>
-      <c r="M35" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B1:K1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>